--- a/results/Int All Data -0.1/Rando_9_permute.xlsx
+++ b/results/Int All Data -0.1/Rando_9_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8932734845378623</v>
+        <v>0.8777412115065064</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8962795917046117</v>
+        <v>0.884493623082069</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9022766999719458</v>
+        <v>0.8796564448952287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9044573685232742</v>
+        <v>0.8980545544789487</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9034646841753167</v>
+        <v>0.8986976412956689</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9057575692181532</v>
+        <v>0.8986976412956689</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9116154858758281</v>
+        <v>0.8986976412956689</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9132372299790673</v>
+        <v>0.900319385398908</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9129156865707071</v>
+        <v>0.9006409288072681</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9129156865707071</v>
+        <v>0.9009624722156283</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9132372299790673</v>
+        <v>0.9025701892574289</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9122445456311099</v>
+        <v>0.9016055590323486</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9112799154060295</v>
+        <v>0.9006128746843911</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9132372299790673</v>
+        <v>0.9012980426854269</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.912594143162347</v>
+        <v>0.9019411295021472</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9109583719976693</v>
+        <v>0.8981656919657308</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9193746088607868</v>
+        <v>0.8988789140896437</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9145234036125078</v>
+        <v>0.8982358272729234</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9116295129372667</v>
+        <v>0.8885053626534885</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9142439413884633</v>
+        <v>0.89490925570254</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9136289086946201</v>
+        <v>0.896474891560025</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9139504521029802</v>
+        <v>0.8987256954185459</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9212477610651935</v>
+        <v>0.8993547551738277</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9196119899005157</v>
+        <v>0.8964608644985865</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9147467575907983</v>
+        <v>0.8920703942683268</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9147467575907983</v>
+        <v>0.8914273074516066</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9070858240359092</v>
+        <v>0.8906299229590626</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9060791126265133</v>
+        <v>0.8909795204902997</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.905407971686916</v>
+        <v>0.890643950020501</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9047508578087572</v>
+        <v>0.890643950020501</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9058277045253458</v>
+        <v>0.8914823366926348</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9064848184035046</v>
+        <v>0.892098448391204</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9058417315867844</v>
+        <v>0.8924199917995641</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9055482423013013</v>
+        <v>0.8931051598005999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9035628736053865</v>
+        <v>0.8927836163922398</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9070998510973478</v>
+        <v>0.8921113964479164</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9070998510973478</v>
+        <v>0.8914262284468806</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9087075681391484</v>
+        <v>0.8920412611407238</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9107209909579403</v>
+        <v>0.8920412611407238</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9136569628174971</v>
+        <v>0.8920412611407238</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.915348842227929</v>
+        <v>0.8923347504262069</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.922059172619176</v>
+        <v>0.8923347504262069</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9217376292108159</v>
+        <v>0.892656293834567</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9230238028442566</v>
+        <v>0.8922786421804527</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9245052763331103</v>
+        <v>0.8916075012408555</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9245052763331103</v>
+        <v>0.8978570966140832</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9272869505168433</v>
+        <v>0.8995349489630764</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9266158095772459</v>
+        <v>0.8913981743240036</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9231349403310387</v>
+        <v>0.8990029996331383</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9210794363279311</v>
+        <v>0.8993105159800601</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9201148061028508</v>
+        <v>0.8993105159800601</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9240294352489264</v>
+        <v>0.9097261486005309</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9240294352489264</v>
+        <v>0.9059787651869915</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9300686247005763</v>
+        <v>0.9091801722091543</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.9396318435874749</v>
+        <v>0.9038250717538143</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.9435723688469755</v>
+        <v>0.8912978268844818</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.9284015623988433</v>
+        <v>0.8865868922505881</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.9334772006301388</v>
+        <v>0.8922624571095621</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.9324985433436199</v>
+        <v>0.8925840005179222</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.935071969615227</v>
+        <v>0.8947096398282224</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.9335203608191804</v>
+        <v>0.8934936015019745</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.9337857959817863</v>
+        <v>0.8934936015019745</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.9023543883122208</v>
+        <v>0.892710244070869</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.9036966701914154</v>
+        <v>0.8895228641101448</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.9023565463216729</v>
+        <v>0.9017145385096786</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.9133181553335203</v>
+        <v>0.8989458123826582</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.9133181553335203</v>
+        <v>0.9035315824683312</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.9079641338829063</v>
+        <v>0.9008610457713805</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8963874921772157</v>
+        <v>0.9049429206499924</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8938852802175273</v>
+        <v>0.9046494313645094</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8850752066294051</v>
+        <v>0.8966389002783832</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8850752066294051</v>
+        <v>0.8980793715876476</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8893825934957595</v>
+        <v>0.8951013185437753</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8913258810073588</v>
+        <v>0.880462461425581</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8954509160750124</v>
+        <v>0.876855348626427</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8891872936403462</v>
+        <v>0.8812879000410022</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8904454131509096</v>
+        <v>0.8801689721400979</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8825762316838948</v>
+        <v>0.8811616564880554</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8822406612140961</v>
+        <v>0.8696400440233929</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8851906601350914</v>
+        <v>0.8674582964673385</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8838494572606228</v>
+        <v>0.8874943352251883</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8873303265068302</v>
+        <v>0.8941107922052699</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8828136127236237</v>
+        <v>0.8888560391894517</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8825201234381406</v>
+        <v>0.8949232827639786</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.8814411187121</v>
+        <v>0.8849834912276916</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.797799909363603</v>
+        <v>0.8849834912276916</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8006938000388442</v>
+        <v>0.8840188610026112</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8358477740132502</v>
+        <v>0.8747221562830445</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8214301128638943</v>
+        <v>0.8756587323852478</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8200489868145622</v>
+        <v>0.8759522216707309</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.8157836811325234</v>
+        <v>0.8733798744038499</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7983750188825827</v>
+        <v>0.8698148427890113</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7983750188825827</v>
+        <v>0.8556949869440429</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.8073102570189257</v>
+        <v>0.8620416927426142</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.8116165648805542</v>
+        <v>0.8611989900515764</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.8031841429465461</v>
+        <v>0.8506161116985692</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.8031841429465461</v>
+        <v>0.8290727033384406</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7961101879626233</v>
+        <v>0.8070405058374155</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7395962364315156</v>
+        <v>0.8108709726148601</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.74331772373163</v>
+        <v>0.8099203694512183</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6894289906989792</v>
+        <v>0.8105634562679385</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6881848982498543</v>
+        <v>0.8105634562679385</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7095027946222404</v>
+        <v>0.8242635792744772</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6512645935389196</v>
+        <v>0.8189203478711238</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6457508793888518</v>
+        <v>0.8088683398433285</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6717948164612961</v>
+        <v>0.80095384017782</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6394311487084313</v>
+        <v>0.7418632253609271</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6420736312825051</v>
+        <v>0.7418632253609271</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6449405468395952</v>
+        <v>0.6729720106174065</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6449686009624722</v>
+        <v>0.684913355920499</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6568700230907012</v>
+        <v>0.6628433932540625</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6400375493644662</v>
+        <v>0.6752465525799003</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6408058007294072</v>
+        <v>0.6440072077515699</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6448175403008265</v>
+        <v>0.6440072077515699</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.623142493364121</v>
+        <v>0.6440072077515699</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5562798075055568</v>
+        <v>0.6762651330412828</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5602365178359481</v>
+        <v>0.7814842789011416</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4957336153132351</v>
+        <v>0.7811346813699044</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5219027169339001</v>
+        <v>0.7834696475970565</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5206165433004597</v>
+        <v>0.7757763439003863</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5177226526252185</v>
+        <v>0.7324715682254688</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5401076846716588</v>
+        <v>0.7700425127862061</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5401076846716588</v>
+        <v>0.7966442953020134</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5234079285267269</v>
+        <v>0.7966442953020134</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5234079285267269</v>
+        <v>0.7978171734392197</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5274757763439004</v>
+        <v>0.7978171734392197</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5301905522346188</v>
+        <v>0.7677701288331643</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5248775329635944</v>
+        <v>0.6667860765230151</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4829441722954746</v>
+        <v>0.6299402231381773</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4654977448801226</v>
+        <v>0.6314648568160728</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4699432443514103</v>
+        <v>0.6135922225339348</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4831502621981484</v>
+        <v>0.6155214829840955</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.48345777854507</v>
+        <v>0.577359243833488</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4829409352812966</v>
+        <v>0.5754440104447658</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4562409633354194</v>
+        <v>0.566674939036233</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4609152118086277</v>
+        <v>0.5780681499384968</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4474934720214074</v>
+        <v>0.5764744599581346</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.3901281857614536</v>
+        <v>0.6089751613112065</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.3869418848054554</v>
+        <v>0.5756727594466864</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.3859632275189365</v>
+        <v>0.5650704590086104</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4054932130602732</v>
+        <v>0.564077774660653</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5051112453872548</v>
+        <v>0.5541638792377911</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4712013638619737</v>
+        <v>0.5115971427954854</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4652582058309416</v>
+        <v>0.4858984872353741</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5200608558665487</v>
+        <v>0.4118679729817216</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4797319752260515</v>
+        <v>0.4125056647748117</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4797319752260515</v>
+        <v>0.4440816590776667</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4777617125963012</v>
+        <v>0.4440956861391053</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4758324521461404</v>
+        <v>0.4786637605472712</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4779861455793176</v>
+        <v>0.4846058395735774</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4909881525281081</v>
+        <v>0.4635005071322212</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4980610285073048</v>
+        <v>0.4669533222555515</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5097390966572434</v>
+        <v>0.47184552968342</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.510074667127042</v>
+        <v>0.5138824748052396</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.510605537452254</v>
+        <v>0.4959602063057036</v>
       </c>
     </row>
   </sheetData>
